--- a/src/preactivador/preactivador.xlsx
+++ b/src/preactivador/preactivador.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\TeamComunicaciones\automatizadorteam\src\preactivador\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo Jaramillo\source\repos\Team\Pruebas\Poliedro Despliegues\Integrateam\src\preactivador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{437C3D3F-784D-4A7B-9C81-34E7A88318E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA7F035-6F5F-4D5E-B755-E4D011CED0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="750" yWindow="3015" windowWidth="13005" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Iccid</t>
   </si>
   <si>
-    <t>Nit</t>
+    <t>Documento</t>
+  </si>
+  <si>
+    <t>TipoDoc</t>
   </si>
   <si>
     <t>Cedula</t>
@@ -35,6 +38,18 @@
   </si>
   <si>
     <t>Mensaje</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 57101602402358561</t>
+  </si>
+  <si>
+    <t>cc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 57101602508054274</t>
+  </si>
+  <si>
+    <t>nit</t>
   </si>
 </sst>
 </file>
@@ -397,10 +412,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -415,6 +437,43 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>1128440365</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2">
+        <v>1038626820</v>
+      </c>
+      <c r="E2">
+        <v>3102856769</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>900910667</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>1038626820</v>
+      </c>
+      <c r="E3">
+        <v>3102868710</v>
       </c>
     </row>
   </sheetData>

--- a/src/preactivador/preactivador.xlsx
+++ b/src/preactivador/preactivador.xlsx
@@ -1,73 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo Jaramillo\source\repos\Team\Pruebas\Poliedro Despliegues\Integrateam\src\preactivador\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA7F035-6F5F-4D5E-B755-E4D011CED0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>Iccid</t>
-  </si>
-  <si>
-    <t>Documento</t>
-  </si>
-  <si>
-    <t>TipoDoc</t>
-  </si>
-  <si>
-    <t>Cedula</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Mensaje</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 57101602402358561</t>
-  </si>
-  <si>
-    <t>cc</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 57101602508054274</t>
-  </si>
-  <si>
-    <t>nit</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -78,7 +52,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -86,44 +60,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -202,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -236,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -270,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -405,78 +351,2541 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.44140625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G108"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>1128440365</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2">
-        <v>1038626820</v>
-      </c>
-      <c r="E2">
-        <v>3102856769</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>900910667</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
-        <v>1038626820</v>
-      </c>
-      <c r="E3">
-        <v>3102868710</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Iccid</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Documento</v>
+      </c>
+      <c r="C1" t="str">
+        <v>TipoDoc</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Cedula</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Min</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Mensaje</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Codigo_distribuidor</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v xml:space="preserve"> 57101702407858818</v>
+      </c>
+      <c r="B2" t="str">
+        <v>66827615</v>
+      </c>
+      <c r="C2" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D2" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E2" t="str">
+        <v>error</v>
+      </c>
+      <c r="F2" t="str">
+        <v>ICC_ID - Identificación Tarjeta de Circuito Integrada.</v>
+      </c>
+      <c r="G2" t="str">
+        <v>D1399.00001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v xml:space="preserve"> 57101702407858847</v>
+      </c>
+      <c r="B3" t="str">
+        <v>71275174</v>
+      </c>
+      <c r="C3" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D3" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E3" t="str">
+        <v>error</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Validacion Causal Desactivacion IccId = Falso</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v xml:space="preserve"> 57101702407858900</v>
+      </c>
+      <c r="B4" t="str">
+        <v>1098668264</v>
+      </c>
+      <c r="C4" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D4" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E4" t="str">
+        <v>3103296339</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v xml:space="preserve"> 57101702407858829</v>
+      </c>
+      <c r="B5" t="str">
+        <v>37775012</v>
+      </c>
+      <c r="C5" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D5" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v xml:space="preserve"> 57101702407858888</v>
+      </c>
+      <c r="B6" t="str">
+        <v>1103101467</v>
+      </c>
+      <c r="C6" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D6" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E6" t="str">
+        <v>3103283558</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v xml:space="preserve"> 57101702407858873</v>
+      </c>
+      <c r="B7" t="str">
+        <v>56083210</v>
+      </c>
+      <c r="C7" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D7" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v xml:space="preserve"> 57101702407858859</v>
+      </c>
+      <c r="B8" t="str">
+        <v>1026163131</v>
+      </c>
+      <c r="C8" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D8" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E8" t="str">
+        <v>3103276324</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v xml:space="preserve"> 57101702407858852</v>
+      </c>
+      <c r="B9" t="str">
+        <v>80772945</v>
+      </c>
+      <c r="C9" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D9" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v xml:space="preserve"> 57101702407858827</v>
+      </c>
+      <c r="B10" t="str">
+        <v>25248951</v>
+      </c>
+      <c r="C10" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D10" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v xml:space="preserve"> 57101702407858832</v>
+      </c>
+      <c r="B11" t="str">
+        <v>1087423122</v>
+      </c>
+      <c r="C11" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D11" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E11" t="str">
+        <v>3103276447</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v xml:space="preserve"> 57101702407858835</v>
+      </c>
+      <c r="B12" t="str">
+        <v>1121889408</v>
+      </c>
+      <c r="C12" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D12" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E12" t="str">
+        <v>error</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Validacion Causal Desactivacion IccId = Falso</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v xml:space="preserve"> 57101702407858898</v>
+      </c>
+      <c r="B13" t="str">
+        <v>21202761</v>
+      </c>
+      <c r="C13" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D13" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E13" t="str">
+        <v>3103295662</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v xml:space="preserve"> 57101702407858879</v>
+      </c>
+      <c r="B14" t="str">
+        <v>52181983</v>
+      </c>
+      <c r="C14" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D14" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E14" t="str">
+        <v>3103319156</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v xml:space="preserve"> 57101702407858902</v>
+      </c>
+      <c r="B15" t="str">
+        <v>1065581367</v>
+      </c>
+      <c r="C15" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D15" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E15" t="str">
+        <v>3103297709</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v xml:space="preserve"> 57101702407858856</v>
+      </c>
+      <c r="B16" t="str">
+        <v>19003289</v>
+      </c>
+      <c r="C16" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D16" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E16" t="str">
+        <v>3103319265</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v xml:space="preserve"> 57101702407858907</v>
+      </c>
+      <c r="B17" t="str">
+        <v>52292111</v>
+      </c>
+      <c r="C17" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D17" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E17" t="str">
+        <v>3103318319</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v xml:space="preserve"> 57101702407858842</v>
+      </c>
+      <c r="B18" t="str">
+        <v>33307724</v>
+      </c>
+      <c r="C18" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D18" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E18" t="str">
+        <v>error</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Validacion Causal Desactivacion IccId = Falso</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v xml:space="preserve"> 57101702407858841</v>
+      </c>
+      <c r="B19" t="str">
+        <v>17849077</v>
+      </c>
+      <c r="C19" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D19" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E19" t="str">
+        <v>error</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Validacion Causal Desactivacion IccId = Falso</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v xml:space="preserve"> 57101702407858850</v>
+      </c>
+      <c r="B20" t="str">
+        <v>40730459</v>
+      </c>
+      <c r="C20" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D20" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E20" t="str">
+        <v>3103303781</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v xml:space="preserve"> 57101702407858871</v>
+      </c>
+      <c r="B21" t="str">
+        <v>1143951860</v>
+      </c>
+      <c r="C21" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D21" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E21" t="str">
+        <v>3103293088</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v xml:space="preserve"> 57101702407858864</v>
+      </c>
+      <c r="B22" t="str">
+        <v>1024487611</v>
+      </c>
+      <c r="C22" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D22" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E22" t="str">
+        <v>3103285329</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v xml:space="preserve"> 57101702407858869</v>
+      </c>
+      <c r="B23" t="str">
+        <v>1050735251</v>
+      </c>
+      <c r="C23" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D23" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E23" t="str">
+        <v>3103276073</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v xml:space="preserve"> 57101702407858866</v>
+      </c>
+      <c r="B24" t="str">
+        <v>1075650955</v>
+      </c>
+      <c r="C24" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D24" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E24" t="str">
+        <v>3103295040</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v xml:space="preserve"> 57101702407858896</v>
+      </c>
+      <c r="B25" t="str">
+        <v>1128407770</v>
+      </c>
+      <c r="C25" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D25" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E25" t="str">
+        <v>3103308468</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v xml:space="preserve"> 57101702407858822</v>
+      </c>
+      <c r="B26" t="str">
+        <v>11299892</v>
+      </c>
+      <c r="C26" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D26" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E26" t="str">
+        <v>error</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Validacion Causal Desactivacion IccId = Falso</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v xml:space="preserve"> 57101702407858851</v>
+      </c>
+      <c r="B27" t="str">
+        <v>32662798</v>
+      </c>
+      <c r="C27" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D27" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E27" t="str">
+        <v>3103292552</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v xml:space="preserve"> 57101702407858877</v>
+      </c>
+      <c r="B28" t="str">
+        <v>47431626</v>
+      </c>
+      <c r="C28" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D28" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E28" t="str">
+        <v>3103316546</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v xml:space="preserve"> 57101702407858855</v>
+      </c>
+      <c r="B29" t="str">
+        <v>57443393</v>
+      </c>
+      <c r="C29" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D29" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E29" t="str">
+        <v>3103293270</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v xml:space="preserve"> 57101702407858966</v>
+      </c>
+      <c r="B30" t="str">
+        <v>80312545</v>
+      </c>
+      <c r="C30" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D30" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E30" t="str">
+        <v>3103305025</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v xml:space="preserve"> 57101702407859007</v>
+      </c>
+      <c r="B31" t="str">
+        <v>1109494591</v>
+      </c>
+      <c r="C31" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D31" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v xml:space="preserve"> 57101702407858956</v>
+      </c>
+      <c r="B32" t="str">
+        <v>73083952</v>
+      </c>
+      <c r="C32" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D32" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v xml:space="preserve"> 57101702407858948</v>
+      </c>
+      <c r="B33" t="str">
+        <v>96168755</v>
+      </c>
+      <c r="C33" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D33" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v xml:space="preserve"> 57101702407859009</v>
+      </c>
+      <c r="B34" t="str">
+        <v>91044113</v>
+      </c>
+      <c r="C34" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D34" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v xml:space="preserve"> 57101702407859000</v>
+      </c>
+      <c r="B35" t="str">
+        <v>36165661</v>
+      </c>
+      <c r="C35" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D35" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v xml:space="preserve"> 57101702407858991</v>
+      </c>
+      <c r="B36" t="str">
+        <v>1036929406</v>
+      </c>
+      <c r="C36" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D36" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v xml:space="preserve"> 57101702407859013</v>
+      </c>
+      <c r="B37" t="str">
+        <v>31991878</v>
+      </c>
+      <c r="C37" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D37" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v xml:space="preserve"> 57101702407858981</v>
+      </c>
+      <c r="B38" t="str">
+        <v>1106454035</v>
+      </c>
+      <c r="C38" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D38" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v xml:space="preserve"> 57101702407858992</v>
+      </c>
+      <c r="B39" t="str">
+        <v>1192760650</v>
+      </c>
+      <c r="C39" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D39" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v xml:space="preserve"> 57101702407858957</v>
+      </c>
+      <c r="B40" t="str">
+        <v>18926305</v>
+      </c>
+      <c r="C40" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D40" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v xml:space="preserve"> 57101702407858965</v>
+      </c>
+      <c r="B41" t="str">
+        <v>11349264</v>
+      </c>
+      <c r="C41" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D41" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v xml:space="preserve"> 57101702407858938</v>
+      </c>
+      <c r="B42" t="str">
+        <v>14695499</v>
+      </c>
+      <c r="C42" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D42" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v xml:space="preserve"> 57101702407859011</v>
+      </c>
+      <c r="B43" t="str">
+        <v>80865576</v>
+      </c>
+      <c r="C43" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D43" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v xml:space="preserve"> 57101702407859003</v>
+      </c>
+      <c r="B44" t="str">
+        <v>43669227</v>
+      </c>
+      <c r="C44" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D44" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v xml:space="preserve"> 57101702407859014</v>
+      </c>
+      <c r="B45" t="str">
+        <v>21970492</v>
+      </c>
+      <c r="C45" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D45" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v xml:space="preserve"> 57101702407859005</v>
+      </c>
+      <c r="B46" t="str">
+        <v>63398562</v>
+      </c>
+      <c r="C46" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D46" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v xml:space="preserve"> 57101702407858987</v>
+      </c>
+      <c r="B47" t="str">
+        <v>1118558486</v>
+      </c>
+      <c r="C47" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D47" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v xml:space="preserve"> 57101702407858939</v>
+      </c>
+      <c r="B48" t="str">
+        <v>1073513646</v>
+      </c>
+      <c r="C48" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D48" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v xml:space="preserve"> 57101702407859001</v>
+      </c>
+      <c r="B49" t="str">
+        <v>13853999</v>
+      </c>
+      <c r="C49" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D49" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v xml:space="preserve"> 57101702407859008</v>
+      </c>
+      <c r="B50" t="str">
+        <v>1098624034</v>
+      </c>
+      <c r="C50" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D50" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v xml:space="preserve"> 57101702407858947</v>
+      </c>
+      <c r="B51" t="str">
+        <v>1026565834</v>
+      </c>
+      <c r="C51" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D51" t="str">
+        <v>56056350</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B52" t="str">
+        <v>9862679</v>
+      </c>
+      <c r="C52" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D52" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B53" t="str">
+        <v>9862680</v>
+      </c>
+      <c r="C53" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D53" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B54" t="str">
+        <v>9862681</v>
+      </c>
+      <c r="C54" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D54" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B55" t="str">
+        <v>9862690</v>
+      </c>
+      <c r="C55" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D55" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B56" t="str">
+        <v>9862691</v>
+      </c>
+      <c r="C56" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D56" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B57" t="str">
+        <v>9862705</v>
+      </c>
+      <c r="C57" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D57" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B58" t="str">
+        <v>9862714</v>
+      </c>
+      <c r="C58" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D58" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B59" t="str">
+        <v>9862715</v>
+      </c>
+      <c r="C59" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D59" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B60" t="str">
+        <v>9862716</v>
+      </c>
+      <c r="C60" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D60" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B61" t="str">
+        <v>9862717</v>
+      </c>
+      <c r="C61" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D61" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B62" t="str">
+        <v>9862718</v>
+      </c>
+      <c r="C62" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D62" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B63" t="str">
+        <v>9862720</v>
+      </c>
+      <c r="C63" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D63" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B64" t="str">
+        <v>9862721</v>
+      </c>
+      <c r="C64" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D64" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B65" t="str">
+        <v>9862722</v>
+      </c>
+      <c r="C65" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D65" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B66" t="str">
+        <v>9862724</v>
+      </c>
+      <c r="C66" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D66" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B67" t="str">
+        <v>9862725</v>
+      </c>
+      <c r="C67" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D67" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B68" t="str">
+        <v>9862727</v>
+      </c>
+      <c r="C68" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D68" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B69" t="str">
+        <v>9862730</v>
+      </c>
+      <c r="C69" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D69" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B70" t="str">
+        <v>9862731</v>
+      </c>
+      <c r="C70" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D70" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B71" t="str">
+        <v>9862734</v>
+      </c>
+      <c r="C71" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D71" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B72" t="str">
+        <v>9862735</v>
+      </c>
+      <c r="C72" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D72" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B73" t="str">
+        <v>9862737</v>
+      </c>
+      <c r="C73" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D73" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B74" t="str">
+        <v>9862741</v>
+      </c>
+      <c r="C74" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D74" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B75" t="str">
+        <v>9863035</v>
+      </c>
+      <c r="C75" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D75" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B76" t="str">
+        <v>9878328</v>
+      </c>
+      <c r="C76" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D76" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B77" t="str">
+        <v>9878344</v>
+      </c>
+      <c r="C77" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D77" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B78" t="str">
+        <v>9895058</v>
+      </c>
+      <c r="C78" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D78" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B79" t="str">
+        <v>9911906</v>
+      </c>
+      <c r="C79" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D79" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B80" t="str">
+        <v>9924039</v>
+      </c>
+      <c r="C80" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D80" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B81" t="str">
+        <v>9940106</v>
+      </c>
+      <c r="C81" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D81" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B82" t="str">
+        <v>9971485</v>
+      </c>
+      <c r="C82" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D82" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B83" t="str">
+        <v>9975757</v>
+      </c>
+      <c r="C83" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D83" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v xml:space="preserve"> 57101702511969600</v>
+      </c>
+      <c r="B84" t="str">
+        <v>9977031</v>
+      </c>
+      <c r="C84" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D84" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B85" t="str">
+        <v>9977565</v>
+      </c>
+      <c r="C85" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D85" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B86" t="str">
+        <v>10024278</v>
+      </c>
+      <c r="C86" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D86" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B87" t="str">
+        <v>10051843</v>
+      </c>
+      <c r="C87" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D87" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B88" t="str">
+        <v>10093383</v>
+      </c>
+      <c r="C88" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D88" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B89" t="str">
+        <v>10095043</v>
+      </c>
+      <c r="C89" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D89" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B90" t="str">
+        <v>10102724</v>
+      </c>
+      <c r="C90" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D90" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B91" t="str">
+        <v>10107517</v>
+      </c>
+      <c r="C91" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D91" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B92" t="str">
+        <v>10109078</v>
+      </c>
+      <c r="C92" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D92" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B93" t="str">
+        <v>10109080</v>
+      </c>
+      <c r="C93" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D93" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B94" t="str">
+        <v>10122760</v>
+      </c>
+      <c r="C94" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D94" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B95" t="str">
+        <v>10134741</v>
+      </c>
+      <c r="C95" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D95" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B96" t="str">
+        <v>10139110</v>
+      </c>
+      <c r="C96" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D96" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B97" t="str">
+        <v>10156763</v>
+      </c>
+      <c r="C97" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D97" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B98" t="str">
+        <v>10157782</v>
+      </c>
+      <c r="C98" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D98" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B99" t="str">
+        <v>10188092</v>
+      </c>
+      <c r="C99" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D99" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B100" t="str">
+        <v>10213278</v>
+      </c>
+      <c r="C100" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D100" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B101" t="str">
+        <v>10222238</v>
+      </c>
+      <c r="C101" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D101" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B102" t="str">
+        <v>10228835</v>
+      </c>
+      <c r="C102" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D102" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B103" t="str">
+        <v>10232386</v>
+      </c>
+      <c r="C103" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D103" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B104" t="str">
+        <v>10234556</v>
+      </c>
+      <c r="C104" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D104" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B105" t="str">
+        <v>10236554</v>
+      </c>
+      <c r="C105" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D105" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B106" t="str">
+        <v>10256645</v>
+      </c>
+      <c r="C106" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D106" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B107" t="str">
+        <v>10268232</v>
+      </c>
+      <c r="C107" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D107" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v xml:space="preserve"> 57101702511969696</v>
+      </c>
+      <c r="B108" t="str">
+        <v>10271210</v>
+      </c>
+      <c r="C108" t="str">
+        <v>cc</v>
+      </c>
+      <c r="D108" t="str">
+        <v>1038626820</v>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
+  </ignoredErrors>
 </worksheet>
 </file>